--- a/picos_raman.xlsx
+++ b/picos_raman.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>966.606</v>
+        <v>958.7534532210698</v>
       </c>
       <c r="BG3" t="inlineStr"/>
     </row>
@@ -4017,11 +4017,11 @@
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>1317.73</v>
+        <v>1286.163341990233</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>260.63</v>
+        <v>1776.153171742524</v>
       </c>
       <c r="BG3" t="inlineStr"/>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>7.464716</v>
+        <v>7.28614895725307</v>
       </c>
       <c r="BG3" t="inlineStr"/>
     </row>
@@ -10187,11 +10187,11 @@
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>9124.609469467117</v>
+        <v>8906.026431519018</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>2070.969011278136</v>
+        <v>13775.721951297</v>
       </c>
       <c r="BG3" t="inlineStr"/>
     </row>
